--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -4521,6 +4521,9 @@
           <cell r="Z1">
             <v>0</v>
           </cell>
+          <cell r="AC1">
+            <v>0</v>
+          </cell>
         </row>
         <row r="38">
           <cell r="R38" t="str">
@@ -8266,10 +8269,16 @@
         <v>46173</v>
       </c>
       <c r="C6" s="147"/>
-      <c r="D6" s="147"/>
+      <c r="D6" s="450" t="inlineStr">
+        <is>
+          <t>Special rate writing down allowance</t>
+        </is>
+      </c>
       <c r="E6" s="147"/>
       <c r="F6" s="147"/>
-      <c r="G6" s="146"/>
+      <c r="G6" s="148">
+        <v>0.06</v>
+      </c>
       <c r="H6" s="147"/>
       <c r="I6" s="450" t="s">
         <v>141</v>
@@ -11272,7 +11281,7 @@
         <v>51</v>
       </c>
       <c r="O80" s="356">
-        <f>IF(([1]Schedule!$R$1+[1]Schedule!$Y$1)&gt;0,[1]Schedule!$R$1+[1]Schedule!$Y$1,0)</f>
+        <f>IF(([1]Schedule!$R$1+[1]Schedule!$Y$1+[1]Schedule!$AC$1)&gt;0,[1]Schedule!$R$1+[1]Schedule!$Y$1+[1]Schedule!$AC$1,0)</f>
         <v>0</v>
       </c>
       <c r="P80" s="357"/>
@@ -17234,7 +17243,10 @@
       <c r="C147" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D147" s="356"/>
+      <c r="D147" s="356">
+        <f>[1]Schedule!$AC$1</f>
+        <v>0</v>
+      </c>
       <c r="E147" s="357"/>
       <c r="F147" s="358"/>
       <c r="G147" s="218" t="s">
@@ -30585,7 +30597,7 @@
         <v>86</v>
       </c>
       <c r="C38" s="128">
-        <f>[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
+        <f>[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$AC$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
         <v>0</v>
       </c>
       <c r="D38" s="23"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -19479,8 +19479,7 @@
         <v>51</v>
       </c>
       <c r="D219" s="356">
-        <f>O179+E197+D210+P190</f>
-        <v>0</v>
+        <f>O179-N(D197)-D210-N(O190)</f>
       </c>
       <c r="E219" s="357"/>
       <c r="F219" s="358"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -18734,8 +18734,7 @@
         <v>51</v>
       </c>
       <c r="O194" s="356">
-        <f>O174</f>
-        <v>0</v>
+        <f>MAX(0,O174-O179+N(D197)+D210+N(O190))</f>
       </c>
       <c r="P194" s="357"/>
       <c r="Q194" s="358"/>
@@ -19479,7 +19478,7 @@
         <v>51</v>
       </c>
       <c r="D219" s="356">
-        <f>O179-N(D197)-D210-N(O190)</f>
+        <f>MAX(0,O179-O174-N(D197)-D210-N(O190))</f>
       </c>
       <c r="E219" s="357"/>
       <c r="F219" s="358"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -4524,6 +4524,15 @@
           <cell r="AC1">
             <v>0</v>
           </cell>
+          <cell r="AE1">
+            <v>0</v>
+          </cell>
+          <cell r="AF1">
+            <v>0</v>
+          </cell>
+          <cell r="AG1">
+            <v>0</v>
+          </cell>
         </row>
         <row r="38">
           <cell r="R38" t="str">
@@ -11418,8 +11427,7 @@
         <v>51</v>
       </c>
       <c r="D85" s="356">
-        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
-        <v>0</v>
+        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
       </c>
       <c r="E85" s="357"/>
       <c r="F85" s="358"/>
@@ -17163,8 +17171,7 @@
         <v>51</v>
       </c>
       <c r="O144" s="356">
-        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
-        <v>0</v>
+        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
       </c>
       <c r="P144" s="357"/>
       <c r="Q144" s="358"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -4503,9 +4503,6 @@
           <cell r="R1">
             <v>0</v>
           </cell>
-          <cell r="S1">
-            <v>0</v>
-          </cell>
           <cell r="V1">
             <v>0</v>
           </cell>
@@ -4530,7 +4527,10 @@
           <cell r="AF1">
             <v>0</v>
           </cell>
-          <cell r="AG1">
+          <cell r="AH1">
+            <v>0</v>
+          </cell>
+          <cell r="AI1">
             <v>0</v>
           </cell>
         </row>
@@ -11427,7 +11427,7 @@
         <v>51</v>
       </c>
       <c r="D85" s="356">
-        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
+        <f>IF(([1]Schedule!$R$1-[1]Schedule!$AE$1+[1]Schedule!$AH$1)&lt;1000,[1]Schedule!$AH$1,0)+IF(([1]Schedule!$AC$1-[1]Schedule!$AF$1+[1]Schedule!$AI$1)&lt;1000,[1]Schedule!$AI$1,0)</f>
       </c>
       <c r="E85" s="357"/>
       <c r="F85" s="358"/>
@@ -17171,7 +17171,7 @@
         <v>51</v>
       </c>
       <c r="O144" s="356">
-        <f>IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
+        <f>IF(([1]Schedule!$R$1-[1]Schedule!$AE$1+[1]Schedule!$AH$1)&lt;1000,[1]Schedule!$AH$1,0)+IF(([1]Schedule!$AC$1-[1]Schedule!$AF$1+[1]Schedule!$AI$1)&lt;1000,[1]Schedule!$AI$1,0)</f>
       </c>
       <c r="P144" s="357"/>
       <c r="Q144" s="358"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -8363,10 +8363,16 @@
         <v>46265</v>
       </c>
       <c r="C9" s="147"/>
-      <c r="D9" s="147"/>
+      <c r="D9" s="450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structures and buildings allowance</t>
+        </is>
+      </c>
       <c r="E9" s="146"/>
       <c r="F9" s="147"/>
-      <c r="G9" s="146"/>
+      <c r="G9" s="148">
+        <v>0.03</v>
+      </c>
       <c r="H9" s="147"/>
       <c r="I9" s="450" t="s">
         <v>122</v>
@@ -8390,10 +8396,16 @@
         <v>46295</v>
       </c>
       <c r="C10" s="147"/>
-      <c r="D10" s="147"/>
+      <c r="D10" s="450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freeport and Investment Zone SBA</t>
+        </is>
+      </c>
       <c r="E10" s="146"/>
       <c r="F10" s="147"/>
-      <c r="G10" s="146"/>
+      <c r="G10" s="148">
+        <v>0.1</v>
+      </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
       <c r="J10" s="147"/>
@@ -17357,16 +17369,24 @@
       <c r="V149" s="220"/>
       <c r="W149" s="243"/>
     </row>
-    <row r="150" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="240"/>
       <c r="B150" s="220"/>
-      <c r="C150" s="227"/>
-      <c r="D150" s="220"/>
-      <c r="E150" s="220"/>
-      <c r="F150" s="220"/>
-      <c r="G150" s="220"/>
-      <c r="H150" s="220"/>
-      <c r="I150" s="220"/>
+      <c r="C150" s="217" t="s">
+        <v>51</v>
+      </c>
+      <c r="D150" s="356"/>
+      <c r="E150" s="357"/>
+      <c r="F150" s="358"/>
+      <c r="G150" s="218" t="s">
+        <v>178</v>
+      </c>
+      <c r="H150" s="219">
+        <v>0</v>
+      </c>
+      <c r="I150" s="219">
+        <v>0</v>
+      </c>
       <c r="J150" s="220"/>
       <c r="K150" s="220"/>
       <c r="L150" s="220"/>
@@ -17383,9 +17403,15 @@
       <c r="W150" s="243"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A151" s="255"/>
+      <c r="A151" s="236">
+        <v>52.1</v>
+      </c>
       <c r="B151" s="220"/>
-      <c r="C151" s="227"/>
+      <c r="C151" s="227" t="inlineStr">
+        <is>
+          <t>Zero-emission car allowance</t>
+        </is>
+      </c>
       <c r="D151" s="227"/>
       <c r="E151" s="227"/>
       <c r="F151" s="227"/>
@@ -17473,12 +17499,12 @@
     </row>
     <row r="154" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A154" s="236">
-        <v>52.1</v>
+        <v>53</v>
       </c>
       <c r="B154" s="220"/>
       <c r="C154" s="227" t="inlineStr">
         <is>
-          <t>Zero-emission car allowance</t>
+          <t>The Structures and Buildings Allowance</t>
         </is>
       </c>
       <c r="D154" s="227"/>
@@ -17495,7 +17521,7 @@
         <v>51</v>
       </c>
       <c r="O154" s="356">
-        <f>D139+D144+D147+D152+D156+D160+O139+O144+O149</f>
+        <f>D139+D144+D147+D150+D152+D156+D160+O139+O144+O149</f>
         <v>0</v>
       </c>
       <c r="P154" s="357"/>
@@ -17544,7 +17570,10 @@
       <c r="C156" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D156" s="356"/>
+      <c r="D156" s="356">
+        <f>[1]Schedule!$K$120</f>
+        <v>0</v>
+      </c>
       <c r="E156" s="331"/>
       <c r="F156" s="332"/>
       <c r="G156" s="218" t="s">
@@ -17579,12 +17608,12 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A157" s="236">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="B157" s="220"/>
       <c r="C157" s="227" t="inlineStr">
         <is>
-          <t>The Structures and Buildings Allowance</t>
+          <t>Freeport and Investment Zones Structures and Buildings Allowance</t>
         </is>
       </c>
       <c r="D157" s="227"/>
@@ -17672,7 +17701,10 @@
       <c r="C160" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D160" s="356"/>
+      <c r="D160" s="356">
+        <f>[1]Schedule!$K$121</f>
+        <v>0</v>
+      </c>
       <c r="E160" s="357"/>
       <c r="F160" s="358"/>
       <c r="G160" s="218" t="s">
@@ -22517,7 +22549,7 @@
       <c r="W324" s="251"/>
     </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="150">
     <mergeCell ref="C298:V323"/>
     <mergeCell ref="A281:W281"/>
     <mergeCell ref="O286:Q286"/>
@@ -22586,6 +22618,7 @@
     <mergeCell ref="G141:H141"/>
     <mergeCell ref="H146:I146"/>
     <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D150:F150"/>
     <mergeCell ref="D152:F152"/>
     <mergeCell ref="D160:F160"/>
     <mergeCell ref="O160:Q160"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -6493,7 +6493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="176" customWidth="1"/>
@@ -7372,10 +7372,7 @@
       <c r="K32" s="181"/>
       <c r="L32" s="181"/>
       <c r="M32" s="181"/>
-      <c r="N32" s="316">
-        <f>Admin!B17</f>
-        <v>46117</v>
-      </c>
+      <c r="N32" s="316"/>
       <c r="O32" s="317"/>
       <c r="P32" s="317"/>
       <c r="Q32" s="318"/>
@@ -8079,18 +8076,621 @@
       <c r="V56" s="206"/>
       <c r="W56" s="207"/>
     </row>
-    <row r="58">
-      <c r="A58" t="s">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A57" s="181"/>
+      <c r="B57" s="181"/>
+      <c r="C57" s="208" t="inlineStr">
+        <is>
+          <t>ENTER: Overlap profit brought forward from earlier years</t>
+        </is>
+      </c>
+      <c r="D57" s="181"/>
+      <c r="E57" s="181"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="181"/>
+      <c r="K57" s="181"/>
+      <c r="L57" s="181"/>
+      <c r="M57" s="181"/>
+      <c r="N57" s="208" t="inlineStr">
+        <is>
+          <t>ENTER: Transition profit not yet treated as arising at the start of this tax year</t>
+        </is>
+      </c>
+      <c r="O57" s="182"/>
+      <c r="P57" s="182"/>
+      <c r="Q57" s="182"/>
+      <c r="R57" s="182"/>
+      <c r="S57" s="182"/>
+      <c r="T57" s="182"/>
+      <c r="U57" s="182"/>
+      <c r="V57" s="182"/>
+      <c r="W57" s="197"/>
+    </row>
+    <row r="58" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="182"/>
+      <c r="B58" s="181"/>
+      <c r="C58" s="201" t="inlineStr">
+        <is>
+          <t> - box 69; the 2023-24 return uses all of it</t>
+        </is>
+      </c>
+      <c r="D58" s="181"/>
+      <c r="E58" s="181"/>
+      <c r="F58" s="181"/>
+      <c r="G58" s="181"/>
+      <c r="H58" s="181"/>
+      <c r="I58" s="181"/>
+      <c r="J58" s="181"/>
+      <c r="K58" s="181"/>
+      <c r="L58" s="182"/>
+      <c r="M58" s="181"/>
+      <c r="N58" s="201" t="inlineStr">
+        <is>
+          <t> - your 2023-24 transition profit less every amount already charged</t>
+        </is>
+      </c>
+      <c r="O58" s="182"/>
+      <c r="P58" s="182"/>
+      <c r="Q58" s="182"/>
+      <c r="R58" s="182"/>
+      <c r="S58" s="182"/>
+      <c r="T58" s="182"/>
+      <c r="U58" s="182"/>
+      <c r="V58" s="182"/>
+      <c r="W58" s="197"/>
+    </row>
+    <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="181"/>
+      <c r="B59" s="181"/>
+      <c r="C59" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" s="328"/>
+      <c r="E59" s="329"/>
+      <c r="F59" s="330"/>
+      <c r="G59" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="H59" s="211">
+        <v>0</v>
+      </c>
+      <c r="I59" s="211">
+        <v>0</v>
+      </c>
+      <c r="J59" s="181"/>
+      <c r="K59" s="181"/>
+      <c r="L59" s="181"/>
+      <c r="M59" s="181"/>
+      <c r="N59" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="O59" s="328"/>
+      <c r="P59" s="331"/>
+      <c r="Q59" s="332"/>
+      <c r="R59" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="S59" s="211">
+        <v>0</v>
+      </c>
+      <c r="T59" s="211">
+        <v>0</v>
+      </c>
+      <c r="U59" s="181"/>
+      <c r="V59" s="181"/>
+      <c r="W59" s="197"/>
+    </row>
+    <row r="60" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="181"/>
+      <c r="B60" s="181"/>
+      <c r="C60" s="181"/>
+      <c r="D60" s="181"/>
+      <c r="E60" s="181"/>
+      <c r="F60" s="181"/>
+      <c r="G60" s="181"/>
+      <c r="H60" s="181"/>
+      <c r="I60" s="181"/>
+      <c r="J60" s="181"/>
+      <c r="K60" s="181"/>
+      <c r="L60" s="181"/>
+      <c r="M60" s="181"/>
+      <c r="N60" s="198"/>
+      <c r="O60" s="198"/>
+      <c r="P60" s="198"/>
+      <c r="Q60" s="198"/>
+      <c r="R60" s="181"/>
+      <c r="S60" s="181"/>
+      <c r="T60" s="181"/>
+      <c r="U60" s="181"/>
+      <c r="V60" s="181"/>
+      <c r="W60" s="197"/>
+    </row>
+    <row r="61" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="182"/>
+      <c r="B61" s="181"/>
+      <c r="C61" s="195" t="inlineStr">
+        <is>
+          <t>Overlap relief used this year</t>
+        </is>
+      </c>
+      <c r="D61" s="181"/>
+      <c r="E61" s="181"/>
+      <c r="F61" s="181"/>
+      <c r="G61" s="181"/>
+      <c r="H61" s="181"/>
+      <c r="I61" s="181"/>
+      <c r="J61" s="181"/>
+      <c r="K61" s="181"/>
+      <c r="L61" s="182"/>
+      <c r="M61" s="181"/>
+      <c r="N61" s="195" t="inlineStr">
+        <is>
+          <t>Transition profit treated as arising this year, before any election</t>
+        </is>
+      </c>
+      <c r="O61" s="182"/>
+      <c r="P61" s="182"/>
+      <c r="Q61" s="182"/>
+      <c r="R61" s="182"/>
+      <c r="S61" s="182"/>
+      <c r="T61" s="182"/>
+      <c r="U61" s="182"/>
+      <c r="V61" s="182"/>
+      <c r="W61" s="197"/>
+    </row>
+    <row r="62" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="182"/>
+      <c r="B62" s="181"/>
+      <c r="C62" s="216" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" s="181"/>
+      <c r="E62" s="181"/>
+      <c r="F62" s="181"/>
+      <c r="G62" s="181"/>
+      <c r="H62" s="181"/>
+      <c r="I62" s="181"/>
+      <c r="J62" s="181"/>
+      <c r="K62" s="181"/>
+      <c r="L62" s="182"/>
+      <c r="M62" s="181"/>
+      <c r="N62" s="216" t="s">
+        <v>181</v>
+      </c>
+      <c r="O62" s="182"/>
+      <c r="P62" s="182"/>
+      <c r="Q62" s="182"/>
+      <c r="R62" s="182"/>
+      <c r="S62" s="182"/>
+      <c r="T62" s="182"/>
+      <c r="U62" s="182"/>
+      <c r="V62" s="182"/>
+      <c r="W62" s="197"/>
+    </row>
+    <row r="63" spans="1:23" ht="4" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="181"/>
+      <c r="B63" s="181"/>
+      <c r="C63" s="181"/>
+      <c r="D63" s="181"/>
+      <c r="E63" s="181"/>
+      <c r="F63" s="181"/>
+      <c r="G63" s="181"/>
+      <c r="H63" s="181"/>
+      <c r="I63" s="181"/>
+      <c r="J63" s="181"/>
+      <c r="K63" s="181"/>
+      <c r="L63" s="181"/>
+      <c r="M63" s="181"/>
+      <c r="N63" s="198"/>
+      <c r="O63" s="198"/>
+      <c r="P63" s="198"/>
+      <c r="Q63" s="198"/>
+      <c r="R63" s="181"/>
+      <c r="S63" s="181"/>
+      <c r="T63" s="181"/>
+      <c r="U63" s="181"/>
+      <c r="V63" s="181"/>
+      <c r="W63" s="197"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="181"/>
+      <c r="B64" s="181"/>
+      <c r="C64" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" s="324">
+        <f>IF(YEAR(Admin!$B$17)=2024,D59,0)</f>
+      </c>
+      <c r="E64" s="325"/>
+      <c r="F64" s="326"/>
+      <c r="G64" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="H64" s="211">
+        <v>0</v>
+      </c>
+      <c r="I64" s="211">
+        <v>0</v>
+      </c>
+      <c r="J64" s="181"/>
+      <c r="K64" s="181"/>
+      <c r="L64" s="181"/>
+      <c r="M64" s="181"/>
+      <c r="N64" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="O64" s="324">
+        <f>IF(YEAR(Admin!$B$17)&lt;2024,0,O59/MAX(1,2029-YEAR(Admin!$B$17)))</f>
+      </c>
+      <c r="P64" s="325"/>
+      <c r="Q64" s="326"/>
+      <c r="R64" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="S64" s="211">
+        <v>0</v>
+      </c>
+      <c r="T64" s="211">
+        <v>0</v>
+      </c>
+      <c r="U64" s="181"/>
+      <c r="V64" s="181"/>
+      <c r="W64" s="197"/>
+    </row>
+    <row r="65" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="181"/>
+      <c r="B65" s="181"/>
+      <c r="C65" s="181"/>
+      <c r="D65" s="181"/>
+      <c r="E65" s="181"/>
+      <c r="F65" s="181"/>
+      <c r="G65" s="181"/>
+      <c r="H65" s="181"/>
+      <c r="I65" s="181"/>
+      <c r="J65" s="181"/>
+      <c r="K65" s="181"/>
+      <c r="L65" s="181"/>
+      <c r="M65" s="181"/>
+      <c r="N65" s="198"/>
+      <c r="O65" s="198"/>
+      <c r="P65" s="198"/>
+      <c r="Q65" s="198"/>
+      <c r="R65" s="181"/>
+      <c r="S65" s="181"/>
+      <c r="T65" s="181"/>
+      <c r="U65" s="181"/>
+      <c r="V65" s="181"/>
+      <c r="W65" s="197"/>
+    </row>
+    <row r="66" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="182"/>
+      <c r="B66" s="181"/>
+      <c r="C66" s="195" t="inlineStr">
+        <is>
+          <t>Overlap profit carried forward</t>
+        </is>
+      </c>
+      <c r="D66" s="181"/>
+      <c r="E66" s="181"/>
+      <c r="F66" s="181"/>
+      <c r="G66" s="181"/>
+      <c r="H66" s="181"/>
+      <c r="I66" s="181"/>
+      <c r="J66" s="181"/>
+      <c r="K66" s="181"/>
+      <c r="L66" s="182"/>
+      <c r="M66" s="181"/>
+      <c r="N66" s="195" t="inlineStr">
+        <is>
+          <t>ENTER: Additional transition profit you elect to treat as arising this year</t>
+        </is>
+      </c>
+      <c r="O66" s="182"/>
+      <c r="P66" s="182"/>
+      <c r="Q66" s="182"/>
+      <c r="R66" s="182"/>
+      <c r="S66" s="182"/>
+      <c r="T66" s="182"/>
+      <c r="U66" s="182"/>
+      <c r="V66" s="182"/>
+      <c r="W66" s="197"/>
+    </row>
+    <row r="67" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="182"/>
+      <c r="B67" s="181"/>
+      <c r="C67" s="216" t="s">
+        <v>181</v>
+      </c>
+      <c r="D67" s="181"/>
+      <c r="E67" s="181"/>
+      <c r="F67" s="181"/>
+      <c r="G67" s="181"/>
+      <c r="H67" s="181"/>
+      <c r="I67" s="181"/>
+      <c r="J67" s="181"/>
+      <c r="K67" s="181"/>
+      <c r="L67" s="182"/>
+      <c r="M67" s="181"/>
+      <c r="N67" s="201" t="inlineStr">
+        <is>
+          <t> - the election itself goes in box 103</t>
+        </is>
+      </c>
+      <c r="O67" s="182"/>
+      <c r="P67" s="182"/>
+      <c r="Q67" s="182"/>
+      <c r="R67" s="182"/>
+      <c r="S67" s="182"/>
+      <c r="T67" s="182"/>
+      <c r="U67" s="182"/>
+      <c r="V67" s="182"/>
+      <c r="W67" s="197"/>
+    </row>
+    <row r="68" spans="1:23" ht="4" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="181"/>
+      <c r="B68" s="181"/>
+      <c r="C68" s="181"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
+      <c r="F68" s="181"/>
+      <c r="G68" s="181"/>
+      <c r="H68" s="181"/>
+      <c r="I68" s="181"/>
+      <c r="J68" s="181"/>
+      <c r="K68" s="181"/>
+      <c r="L68" s="181"/>
+      <c r="M68" s="181"/>
+      <c r="N68" s="198"/>
+      <c r="O68" s="198"/>
+      <c r="P68" s="198"/>
+      <c r="Q68" s="198"/>
+      <c r="R68" s="181"/>
+      <c r="S68" s="181"/>
+      <c r="T68" s="181"/>
+      <c r="U68" s="181"/>
+      <c r="V68" s="181"/>
+      <c r="W68" s="197"/>
+    </row>
+    <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="181"/>
+      <c r="B69" s="181"/>
+      <c r="C69" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="D69" s="324">
+        <f>D59-D64</f>
+      </c>
+      <c r="E69" s="325"/>
+      <c r="F69" s="326"/>
+      <c r="G69" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="H69" s="211">
+        <v>0</v>
+      </c>
+      <c r="I69" s="211">
+        <v>0</v>
+      </c>
+      <c r="J69" s="181"/>
+      <c r="K69" s="181"/>
+      <c r="L69" s="181"/>
+      <c r="M69" s="181"/>
+      <c r="N69" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="O69" s="328"/>
+      <c r="P69" s="331"/>
+      <c r="Q69" s="332"/>
+      <c r="R69" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="S69" s="211">
+        <v>0</v>
+      </c>
+      <c r="T69" s="211">
+        <v>0</v>
+      </c>
+      <c r="U69" s="181"/>
+      <c r="V69" s="181"/>
+      <c r="W69" s="197"/>
+    </row>
+    <row r="70" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="181"/>
+      <c r="B70" s="181"/>
+      <c r="C70" s="181"/>
+      <c r="D70" s="181"/>
+      <c r="E70" s="181"/>
+      <c r="F70" s="181"/>
+      <c r="G70" s="181"/>
+      <c r="H70" s="181"/>
+      <c r="I70" s="181"/>
+      <c r="J70" s="181"/>
+      <c r="K70" s="181"/>
+      <c r="L70" s="181"/>
+      <c r="M70" s="181"/>
+      <c r="N70" s="198"/>
+      <c r="O70" s="198"/>
+      <c r="P70" s="198"/>
+      <c r="Q70" s="198"/>
+      <c r="R70" s="181"/>
+      <c r="S70" s="181"/>
+      <c r="T70" s="181"/>
+      <c r="U70" s="181"/>
+      <c r="V70" s="181"/>
+      <c r="W70" s="197"/>
+    </row>
+    <row r="71" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="182"/>
+      <c r="B71" s="181"/>
+      <c r="C71" s="195" t="inlineStr">
+        <is>
+          <t>ENTER: Profit of your next accounting period, a loss with a minus sign, provisional until its accounts are final</t>
+        </is>
+      </c>
+      <c r="D71" s="181"/>
+      <c r="E71" s="181"/>
+      <c r="F71" s="181"/>
+      <c r="G71" s="181"/>
+      <c r="H71" s="181"/>
+      <c r="I71" s="181"/>
+      <c r="J71" s="181"/>
+      <c r="K71" s="181"/>
+      <c r="L71" s="182"/>
+      <c r="M71" s="181"/>
+      <c r="N71" s="195" t="inlineStr">
+        <is>
+          <t>Transition profit carried forward to next year</t>
+        </is>
+      </c>
+      <c r="O71" s="182"/>
+      <c r="P71" s="182"/>
+      <c r="Q71" s="182"/>
+      <c r="R71" s="182"/>
+      <c r="S71" s="182"/>
+      <c r="T71" s="182"/>
+      <c r="U71" s="182"/>
+      <c r="V71" s="182"/>
+      <c r="W71" s="197"/>
+    </row>
+    <row r="72" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="182"/>
+      <c r="B72" s="181"/>
+      <c r="C72" s="201" t="inlineStr">
+        <is>
+          <t> - only if box 9 is not 31 March to 5 April; box 68 apportions both periods to the tax year by days</t>
+        </is>
+      </c>
+      <c r="D72" s="181"/>
+      <c r="E72" s="181"/>
+      <c r="F72" s="181"/>
+      <c r="G72" s="181"/>
+      <c r="H72" s="181"/>
+      <c r="I72" s="181"/>
+      <c r="J72" s="181"/>
+      <c r="K72" s="181"/>
+      <c r="L72" s="182"/>
+      <c r="M72" s="181"/>
+      <c r="N72" s="216" t="s">
+        <v>181</v>
+      </c>
+      <c r="O72" s="182"/>
+      <c r="P72" s="182"/>
+      <c r="Q72" s="182"/>
+      <c r="R72" s="182"/>
+      <c r="S72" s="182"/>
+      <c r="T72" s="182"/>
+      <c r="U72" s="182"/>
+      <c r="V72" s="182"/>
+      <c r="W72" s="197"/>
+    </row>
+    <row r="73" spans="1:23" ht="4" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="181"/>
+      <c r="B73" s="181"/>
+      <c r="C73" s="181"/>
+      <c r="D73" s="181"/>
+      <c r="E73" s="181"/>
+      <c r="F73" s="181"/>
+      <c r="G73" s="181"/>
+      <c r="H73" s="181"/>
+      <c r="I73" s="181"/>
+      <c r="J73" s="181"/>
+      <c r="K73" s="181"/>
+      <c r="L73" s="181"/>
+      <c r="M73" s="181"/>
+      <c r="N73" s="198"/>
+      <c r="O73" s="198"/>
+      <c r="P73" s="198"/>
+      <c r="Q73" s="198"/>
+      <c r="R73" s="181"/>
+      <c r="S73" s="181"/>
+      <c r="T73" s="181"/>
+      <c r="U73" s="181"/>
+      <c r="V73" s="181"/>
+      <c r="W73" s="197"/>
+    </row>
+    <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="181"/>
+      <c r="B74" s="181"/>
+      <c r="C74" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="D74" s="328"/>
+      <c r="E74" s="329"/>
+      <c r="F74" s="330"/>
+      <c r="G74" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="H74" s="211">
+        <v>0</v>
+      </c>
+      <c r="I74" s="211">
+        <v>0</v>
+      </c>
+      <c r="J74" s="181"/>
+      <c r="K74" s="181"/>
+      <c r="L74" s="181"/>
+      <c r="M74" s="181"/>
+      <c r="N74" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="O74" s="324">
+        <f>O59-O64-O69</f>
+      </c>
+      <c r="P74" s="325"/>
+      <c r="Q74" s="326"/>
+      <c r="R74" s="210" t="s">
+        <v>178</v>
+      </c>
+      <c r="S74" s="211">
+        <v>0</v>
+      </c>
+      <c r="T74" s="211">
+        <v>0</v>
+      </c>
+      <c r="U74" s="181"/>
+      <c r="V74" s="181"/>
+      <c r="W74" s="197"/>
+    </row>
+    <row r="75" spans="1:23" ht="8" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="181"/>
+      <c r="B75" s="181"/>
+      <c r="C75" s="181"/>
+      <c r="D75" s="181"/>
+      <c r="E75" s="181"/>
+      <c r="F75" s="181"/>
+      <c r="G75" s="181"/>
+      <c r="H75" s="181"/>
+      <c r="I75" s="181"/>
+      <c r="J75" s="181"/>
+      <c r="K75" s="181"/>
+      <c r="L75" s="181"/>
+      <c r="M75" s="181"/>
+      <c r="N75" s="198"/>
+      <c r="O75" s="198"/>
+      <c r="P75" s="198"/>
+      <c r="Q75" s="198"/>
+      <c r="R75" s="181"/>
+      <c r="S75" s="181"/>
+      <c r="T75" s="181"/>
+      <c r="U75" s="181"/>
+      <c r="V75" s="181"/>
+      <c r="W75" s="197"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="s">
+    <row r="77">
+      <c r="A77" t="s">
         <v>441</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="34">
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="O55:Q55"/>
@@ -8117,6 +8717,14 @@
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="C7:J7"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="O59:Q59"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="O64:Q64"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="O69:Q69"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="O74:Q74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -18852,11 +19460,11 @@
       <c r="C197" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="D197" s="275" t="s">
-        <v>250</v>
-      </c>
-      <c r="E197" s="375"/>
-      <c r="F197" s="386"/>
+      <c r="D197" s="356">
+        <f>IF(OR('Business Details'!N32="",'Business Details'!N32&gt;=DATE(YEAR(Admin!$B$17),3,31)),0,('Business Details'!N32-MAX('Business Details'!N27,Admin!$B$4)+1)/('Business Details'!N32-'Business Details'!N27+1)*(O174-O179)+(Admin!$B$17-'Business Details'!N32)/(EDATE('Business Details'!N32,12)-'Business Details'!N32)*'Business Details'!D74-(O174-O179))</f>
+      </c>
+      <c r="E197" s="357"/>
+      <c r="F197" s="358"/>
       <c r="G197" s="218" t="s">
         <v>178</v>
       </c>
@@ -18911,11 +19519,13 @@
       <c r="W198" s="243"/>
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A199" s="236"/>
+      <c r="A199" s="236">
+        <v>73.3</v>
+      </c>
       <c r="B199" s="220"/>
       <c r="C199" s="227" t="inlineStr">
         <is>
-          <t>Boxes 69 and 70 are not in use</t>
+          <t>Spread of the transition profit treated as arising in this</t>
         </is>
       </c>
       <c r="D199" s="220"/>
@@ -18953,7 +19563,11 @@
     <row r="200" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="255"/>
       <c r="B200" s="220"/>
-      <c r="C200" s="227"/>
+      <c r="C200" s="227" t="inlineStr">
+        <is>
+          <t>tax year - see the working sheet in the notes</t>
+        </is>
+      </c>
       <c r="D200" s="227"/>
       <c r="E200" s="227"/>
       <c r="F200" s="227"/>
@@ -18978,13 +19592,23 @@
     <row r="201" spans="1:23" ht="16" x14ac:dyDescent="0.15">
       <c r="A201" s="240"/>
       <c r="B201" s="220"/>
-      <c r="C201" s="227"/>
-      <c r="D201" s="227"/>
-      <c r="E201" s="227"/>
-      <c r="F201" s="227"/>
-      <c r="G201" s="218"/>
-      <c r="H201" s="227"/>
-      <c r="I201" s="227"/>
+      <c r="C201" s="217" t="s">
+        <v>51</v>
+      </c>
+      <c r="D201" s="356">
+        <f>'Business Details'!O64+'Business Details'!O69</f>
+      </c>
+      <c r="E201" s="357"/>
+      <c r="F201" s="358"/>
+      <c r="G201" s="218" t="s">
+        <v>178</v>
+      </c>
+      <c r="H201" s="219">
+        <v>0</v>
+      </c>
+      <c r="I201" s="219">
+        <v>0</v>
+      </c>
       <c r="J201" s="220"/>
       <c r="K201" s="220"/>
       <c r="L201" s="236">
@@ -19063,7 +19687,11 @@
     <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="240"/>
       <c r="B204" s="220"/>
-      <c r="C204" s="241"/>
+      <c r="C204" s="227" t="inlineStr">
+        <is>
+          <t>Boxes 69 and 70 are not in use</t>
+        </is>
+      </c>
       <c r="D204" s="220"/>
       <c r="E204" s="220"/>
       <c r="F204" s="220"/>
@@ -22601,7 +23229,7 @@
     <mergeCell ref="C190:F190"/>
     <mergeCell ref="P190:Q190"/>
     <mergeCell ref="O194:Q194"/>
-    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="D197:F197"/>
     <mergeCell ref="D179:F179"/>
     <mergeCell ref="O179:Q179"/>
     <mergeCell ref="A181:W181"/>
@@ -26523,10 +27151,17 @@
     </row>
     <row r="14" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="96"/>
-      <c r="B14" s="108"/>
+      <c r="B14" s="108" t="inlineStr">
+        <is>
+          <t>Income Tax on transition profit (box 73.3), charged as the top slice</t>
+        </is>
+      </c>
       <c r="C14" s="108"/>
       <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
+      <c r="E14" s="99">
+        <f>IF('SE Full'!D201&gt;0,IF(E7+'SE Full'!D201&lt;C9,(E7+'SE Full'!D201)*D8,C9*D8)+IF(E7+'SE Full'!D201&gt;C9,(MIN(E7+'SE Full'!D201,C10)-C9)*D9,0)+IF(E7+'SE Full'!D201&gt;C10,(E7+'SE Full'!D201-C10)*D10,0)-E11,0)</f>
+        <v>0</v>
+      </c>
       <c r="F14" s="122"/>
       <c r="G14" s="121"/>
       <c r="M14" s="293"/>
@@ -26542,7 +27177,7 @@
         <v>0.06</v>
       </c>
       <c r="E15" s="102">
-        <f>IF(E5&gt;Admin!N20,IF(E5&lt;Admin!N$23,(E5-Admin!N20)*D15,(Admin!N$23-Admin!N20)*D15),0)</f>
+        <f>IF((E5+'SE Full'!D201)&gt;Admin!N20,IF((E5+'SE Full'!D201)&lt;Admin!N$23,((E5+'SE Full'!D201)-Admin!N20)*D15,(Admin!N$23-Admin!N20)*D15),0)</f>
         <v>0</v>
       </c>
       <c r="F15" s="122"/>
@@ -26560,7 +27195,7 @@
         <v>0.02</v>
       </c>
       <c r="E16" s="102">
-        <f>IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
+        <f>IF(((E5+'SE Full'!D201)&gt;Admin!N$23),(((E5+'SE Full'!D201)-Admin!N$23)*D16),0)</f>
         <v>0</v>
       </c>
       <c r="F16" s="122"/>

--- a/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Self Employed 2027-04-05 (Apr27) Excel 2007/Financialaccounts.xlsx
@@ -9311,7 +9311,7 @@
         <v>10000</v>
       </c>
       <c r="G21" s="168">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="H21" s="147"/>
       <c r="I21" s="169"/>
